--- a/temp_doc/MAPEL - MPLB.xlsx
+++ b/temp_doc/MAPEL - MPLB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159FED97-71F8-7E47-8919-0D29F123E349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9337C849-902A-5141-80C4-AC8A1A58F784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16120" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F3B5AAF4-EB82-C44B-8005-9A97E3042361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>id_mapel</t>
   </si>
@@ -47,71 +47,125 @@
     <t>nama_mapel</t>
   </si>
   <si>
-    <t>BAHASA INDONESIA ( XII MPLB 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XII MPLB 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( XII MPLB 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XII MPLB 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XII MPLB 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XII MPLB 1 )</t>
-  </si>
-  <si>
-    <t>PEND. PANCASILA DAN KEWARGANEGARAAN ( XII MPLB 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XII MPLB 1 )</t>
-  </si>
-  <si>
-    <t>PRODUK KREATIF DAN KEWIRAUSAHAAN ( XII MPLB 1 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XII MPLB 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XII MPLB 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XII MPLB 2 )</t>
-  </si>
-  <si>
-    <t>PEND. PANCASILA DAN KEWARGANEGARAAN ( XII MPLB 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XII MPLB 2 )</t>
-  </si>
-  <si>
-    <t>PRODUK KREATIF DAN KEWIRAUSAHAAN ( XII MPLB 2 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XII MPLB 2 )</t>
+    <t>AGAMA ISLAM ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>PJOK ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>SENI DAN BUDAYA ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>INFORMATIKA ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>PROJEK IPAS ( X MPLB 1 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>CODING &amp; AI ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>PJOK ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>SENI DAN BUDAYA ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>INFORMATIKA ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>PROJEK IPAS ( X MPLB 2 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>MATA PELAJARAN PILIHAN ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>PJOK ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>PKK ( XI MPLB 1 )</t>
+  </si>
+  <si>
+    <t>AGAMA ISLAM ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>AGAMA KRISTEN ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN PANCASILA ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>JEPANG ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>MATA PELAJARAN PILIHAN ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>PJOK ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>SEJARAH ( XI MPLB 2 )</t>
+  </si>
+  <si>
+    <t>PKK ( XI MPLB 2 )</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF858796"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -136,7 +190,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,12 +525,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E4DC37-752B-FA41-9A64-68D7A3795B3C}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -491,223 +545,401 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1041</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1023</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>30019244</v>
+      </c>
+      <c r="B2">
+        <v>1004</v>
       </c>
       <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>30022227</v>
+      </c>
+      <c r="B3">
+        <v>1004</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>30032390</v>
+      </c>
+      <c r="B4">
+        <v>1004</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>30048020</v>
+      </c>
+      <c r="B5">
+        <v>1004</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>30053299</v>
+      </c>
+      <c r="B6">
+        <v>1004</v>
+      </c>
+      <c r="C6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1042</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1023</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>30067169</v>
+      </c>
+      <c r="B7">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1043</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1023</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1044</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1023</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>30079489</v>
+      </c>
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1045</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1023</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1046</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1023</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>30085597</v>
+      </c>
+      <c r="B9">
+        <v>1004</v>
+      </c>
+      <c r="C9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1047</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1023</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>30092007</v>
+      </c>
+      <c r="B10">
+        <v>1004</v>
+      </c>
+      <c r="C10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1048</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1023</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>30109807</v>
+      </c>
+      <c r="B11">
+        <v>1004</v>
+      </c>
+      <c r="C11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1049</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1024</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>30114118</v>
+      </c>
+      <c r="B12">
+        <v>1005</v>
+      </c>
+      <c r="C12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1050</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1024</v>
-      </c>
-      <c r="C11" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>30125950</v>
+      </c>
+      <c r="B13">
+        <v>1005</v>
+      </c>
+      <c r="C13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>1051</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1024</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1052</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1024</v>
-      </c>
-      <c r="C13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>30137240</v>
+      </c>
+      <c r="B14">
+        <v>1005</v>
+      </c>
+      <c r="C14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1053</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1024</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1054</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1024</v>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>30142970</v>
+      </c>
+      <c r="B15">
+        <v>1005</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>1055</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1024</v>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>30151302</v>
+      </c>
+      <c r="B16">
+        <v>1005</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>1056</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1024</v>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>30162465</v>
+      </c>
+      <c r="B17">
+        <v>1005</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="B31" s="1"/>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>30174489</v>
+      </c>
+      <c r="B18">
+        <v>1005</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>30185024</v>
+      </c>
+      <c r="B19">
+        <v>1005</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>30191323</v>
+      </c>
+      <c r="B20">
+        <v>1005</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>30204753</v>
+      </c>
+      <c r="B21">
+        <v>1005</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>30211625</v>
+      </c>
+      <c r="B22">
+        <v>1014</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>30221189</v>
+      </c>
+      <c r="B23">
+        <v>1014</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>30235956</v>
+      </c>
+      <c r="B24">
+        <v>1014</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>30243929</v>
+      </c>
+      <c r="B25">
+        <v>1014</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>30258267</v>
+      </c>
+      <c r="B26">
+        <v>1014</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>30264649</v>
+      </c>
+      <c r="B27">
+        <v>1014</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>30271467</v>
+      </c>
+      <c r="B28">
+        <v>1014</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>30282968</v>
+      </c>
+      <c r="B29">
+        <v>1014</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>30297124</v>
+      </c>
+      <c r="B30">
+        <v>1015</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30304045</v>
+      </c>
+      <c r="B31">
+        <v>1015</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>30316723</v>
+      </c>
+      <c r="B32">
+        <v>1015</v>
+      </c>
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>30329425</v>
+      </c>
+      <c r="B33">
+        <v>1015</v>
+      </c>
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>30333531</v>
+      </c>
+      <c r="B34">
+        <v>1015</v>
+      </c>
+      <c r="C34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>30344326</v>
+      </c>
+      <c r="B35">
+        <v>1015</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>30359159</v>
+      </c>
+      <c r="B36">
+        <v>1015</v>
+      </c>
+      <c r="C36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>30361156</v>
+      </c>
+      <c r="B37">
+        <v>1015</v>
+      </c>
+      <c r="C37" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
